--- a/daily_matches/job_matches_2026-05-08.xlsx
+++ b/daily_matches/job_matches_2026-05-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Junior Automation Engineer (Cloud)</t>
+          <t>Site Reliability Engineer III</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.8</v>
+        <v>15.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>S3, EC2, Glue, Athena, Redshift, Data Lake, CI/CD, GitHub Actions, Terraform, Git</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Snowflake, Databricks, Python</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23fd00a4507ab066</t>
+          <t>https://www.indeed.com/viewjob?jk=39123815bfb490a9</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Junior Automation Engineer (Cloud)</t>
+          <t>Senior Software Engineer, Full Stack</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CoBank</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Greenwood Village, CO, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>12.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Hugging Face, Prompt Engineering, PySpark, PostgreSQL, MongoDB, NoSQL, Python</t>
+          <t>Generative AI, RAG, TensorFlow, Docker, Kubernetes, CI/CD, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,67 +531,67 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4ebde076d2f48a0</t>
+          <t>https://www.indeed.com/viewjob?jk=a00c6df2acb90b04</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sr. Machine Learning Engineer</t>
+          <t>Engineer, Software Engineer - Entry Level - Java, Angular, or Python</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Canoe Intelligence</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Copilot, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Git, Python, R</t>
+          <t>RAG, Copilot, Kubernetes, GitHub Actions, Git, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adbd88830bdd0bdb</t>
+          <t>https://www.indeed.com/viewjob?jk=b79944ab8184c058</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AWS Systems Engineer</t>
+          <t>L1 SRE Operations Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Dallas-Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, CI/CD, Terraform, NoSQL, Python, SQL, R, Java</t>
+          <t>RAG, EC2, Kubernetes, Kafka, NoSQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,462 +601,42 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53af07e478e3cd7d</t>
+          <t>https://www.indeed.com/viewjob?jk=f389d60ba30d07cb</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Software Engineer III-ETL/PySpark</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, EC2, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, SQL, R</t>
+          <t>RAG, CI/CD, Git, Snowflake, PySpark, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd5d72a84ca4e4ea</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Junior Automation Engineer (Cloud)</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, S3, FastAPI, Git, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e6f28234b7507720</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Data Scientist, Growth &amp; Measurement</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Data Scientist, Redshift, BigQuery, Snowflake, BigQuery, Redshift, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d596de1b93140484</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Data Scientist – Transmission ROW Risk Analytics</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Global Software Resources</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Dublin, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Data Scientist, Tableau, Power BI, Matplotlib, Seaborn, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=de4935dd718f61e0</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer (HYBRID)</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>C-4 Analytics</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Wakefield, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Git, Snowflake, MongoDB, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2bf7e0b35f8ea7b1</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer (C, C++, Linux, Rest API)</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Rocket Software</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Docker, Git, PostgreSQL, SQL, R, Java, C++, Scala</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9469e0cd63d5176e</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Sr Analyst-Advanced Analytics &amp; BI</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>The Walt Disney Company</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Celebration, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>RAG, XGBoost, LightGBM, Git, Snowflake, Tableau, Python, SQL, R, A/B Testing</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e476093767a3bff4</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Artificial Intelligence Engineer I</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Baylor College of Medicine</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>10</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>AI Engineer, TensorFlow, PyTorch, Docker, Kubernetes, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d2c6285d914a14f3</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Artificial Intelligence Engineer I</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Baylor College of Medicine</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>10</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>AI Engineer, TensorFlow, PyTorch, Docker, Kubernetes, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7576adfa506ecdfd</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Senior Machine Learning Research Scientist</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>SmarterDx</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>10</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>PyTorch, AWS SageMaker, Kubernetes, Apache Airflow, Git, Snowflake, Python, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=40314227d60dc803</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Junior Automation Engineer (Cloud)</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>10</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>RAG, Data Lake, CI/CD, Databricks, PySpark, Kafka, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=30a75c1c6a28610f</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Senior Data &amp; Analytics (ML-Enabled Systems)</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Thomson Reuters</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Eagan, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>10</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Generative AI, Data Lake, Git, Snowflake, Power BI, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c5c6286b6172c83b</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Senior Data Scientist</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>SmarterDx</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>10</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, Snowflake, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=760b3abe0905b05f</t>
+          <t>https://www.indeed.com/viewjob?jk=2032a94f0b2c0e2c</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-05-08.xlsx
+++ b/daily_matches/job_matches_2026-05-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer III</t>
+          <t>Kubernetes Operations Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>15.6</v>
+        <v>24.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Snowflake, Databricks, Python</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Copilot, Hugging Face, ChromaDB, Prompt Engineering, TensorFlow</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,137 +496,137 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39123815bfb490a9</t>
+          <t>https://www.indeed.com/viewjob?jk=72afaba96f57d60e</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Full Stack</t>
+          <t>AWS Systems Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CoBank</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Greenwood Village, CO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>12.2</v>
+        <v>24.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, TensorFlow, Docker, Kubernetes, CI/CD, Git, Python, SQL, R</t>
+          <t>Data Scientist, TensorFlow, PyTorch, AWS SageMaker, S3, Glue, Athena, Redshift, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a00c6df2acb90b04</t>
+          <t>https://www.indeed.com/viewjob?jk=81fe8958cd4a14a2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Engineer, Software Engineer - Entry Level - Java, Angular, or Python</t>
+          <t>AI Technical Architect - Onsite</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>NTT Global Data Centers Americas, Inc.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>11.1</v>
+        <v>23.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, GitHub Actions, Git, Python, SQL, R, Java, Scala</t>
+          <t>LangChain, RAG, Pinecone, Prompt Engineering, S3, Athena, Redshift, Kinesis, FastAPI, Docker</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b79944ab8184c058</t>
+          <t>https://www.indeed.com/viewjob?jk=7327c0bf569365fa</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>L1 SRE Operations Engineer</t>
+          <t>Junior Automation Engineer (Cloud)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dallas-Fort Worth, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>18.9</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, EC2, Kubernetes, Kafka, NoSQL, Python, SQL, R, Scala</t>
+          <t>S3, EC2, Glue, Athena, Redshift, Data Lake, CI/CD, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f389d60ba30d07cb</t>
+          <t>https://www.indeed.com/viewjob?jk=5335254820a6db07</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer III-ETL/PySpark</t>
+          <t>AWS Systems Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>17.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Git, Snowflake, PySpark, Python, SQL, R, Scala</t>
+          <t>Copilot, S3, EC2, FastAPI, Docker, Kubernetes, CI/CD, Terraform, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,7 +636,3297 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2032a94f0b2c0e2c</t>
+          <t>https://www.indeed.com/viewjob?jk=587fb03845771fd7</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Kubernetes Administrator</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d34578ddc24426b1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Senior Kubernetes Security Engineer</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Pinecone, Prompt Engineering, Docker, Kubernetes, NoSQL</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=38faaa7e75d7656a</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>SENIOR PYTHON SOFTWARE ENGINEER</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Brightgrove</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>LangChain, Copilot, TensorFlow, PyTorch, S3, Kubernetes, Git, PostgreSQL, NoSQL, Python</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9ac0a3b244a9e118</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, BigQuery, FastAPI, Docker, CI/CD, Terraform, BigQuery, PySpark, Hadoop</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=78d7d81277bb81ba</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>AWS Technical Apprentice / Trainee</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Copilot, Glue, Docker, CI/CD, Jenkins, Git, Snowflake, PostgreSQL, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c43b6c07f7a10c25</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>KAYAK</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Concord, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>RAG, Redshift, Docker, CI/CD, GitHub Actions, Git, Redshift, Kafka, MySQL, Python</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=590a93b85ac25dec</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Senior AI Application Engineer</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Analog Devices</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Wilmington, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Copilot, Pinecone, Prompt Engineering, CI/CD, Git, Python</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b5001197e96c3947</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Data Scientist, S3, EC2, Docker, Kubernetes, CI/CD, Terraform, Git, R, Java</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2ab9df159e473dcf</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Senior SRE (Kubernetes)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>RAG, EC2, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, SQL, R</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f2d3d34de1eead8b</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Cloud Support Associate</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0077323c8678a550</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Senior Engineer, Supply Chain Systems (Remote)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Abercrombie &amp; Fitch</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Copilot, Docker, Kubernetes, CI/CD, Git, Kafka, MySQL, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0c89ce135bb4639d</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Sr Analyst-Advanced Analytics &amp; BI</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Disney Experiences</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Celebration, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>RAG, XGBoost, LightGBM, Git, Snowflake, Tableau, Python, SQL, R, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f43f5d7e9941863d</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Java Backend Developer - GCP, GraphQL</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>LTIMindtree</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Cincinnati, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, Git, Kafka, PostgreSQL, NoSQL, SQL, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=234380b23def2cb2</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Senior DevOps Engineer (Kubernetes)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, Terraform, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1d89c117f1e086cd</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence Engineer</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>GRP Solutions</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Texas City, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>10</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5718b5011d7465dc</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Senior DevOps Engineer (Kubernetes)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>10</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=087ab144e97379ba</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Kubernetes CI/CD Engineer</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>10</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Kubernetes, CI/CD, Jenkins, Terraform, Git, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c41dfe228e3f8361</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Senior Kubernetes Engineer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Docker, Kubernetes, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c6de2fd4f79b0a84</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>SRE (Kubernetes)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>10</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, CI/CD, GitHub Actions, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=474158839a7b550a</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Cloud Support Engineer (Containers)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>10</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=85f537fcf871abc5</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Kubernetes Security Engineer</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>10</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=05932e2bdc0b6ca7</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>GenAI Python Systems Engineer – Senior Associate</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Portland, OR, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>10</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Data Lake, Docker, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4e4bedeadb55550d</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>GenAI Python Systems Engineer – Senior Associate</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Data Lake, Docker, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a86bba0f9e4d818a</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>GenAI Python Systems Engineer – Senior Associate</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>10</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Data Lake, Docker, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ea2dfcc5c2adecc9</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>GenAI Python Systems Engineer – Senior Associate</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Little Rock, AR, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>10</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Data Lake, Docker, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=312f9634917652f9</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>GenAI Python Systems Engineer – Senior Associate</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>10</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Data Lake, Docker, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2cc625ea8822cae5</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>GenAI Python Systems Engineer – Senior Associate</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Las Vegas, NV, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>10</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Data Lake, Docker, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ce3a0c657a123463</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>GenAI Python Systems Engineer – Senior Associate</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Florham Park, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>10</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Data Lake, Docker, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7313777d2d9eb264</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>GenAI Python Systems Engineer – Senior Associate</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Kansas City, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>10</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Data Lake, Docker, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1c4ea4454f747410</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>GenAI Python Systems Engineer – Senior Associate</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Birmingham, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>10</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Data Lake, Docker, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c385e203695a4a7a</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>GenAI Python Systems Engineer – Senior Associate</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Fayetteville, AR, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>10</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Data Lake, Docker, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=854b0c53a4ee03d0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>GenAI Python Systems Engineer – Senior Associate</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>10</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Data Lake, Docker, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d6086f59372b3530</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>GenAI Python Systems Engineer – Senior Associate</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>10</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Data Lake, Docker, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3d617c884b1f41e1</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>GenAI Python Systems Engineer – Senior Associate</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Detroit, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>10</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Data Lake, Docker, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=43ecfe71c9420e92</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>GenAI Python Systems Engineer – Senior Associate</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>10</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Data Lake, Docker, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ea6ec48d315038e5</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>GenAI Python Systems Engineer – Senior Associate</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Irvine, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>10</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Data Lake, Docker, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=87eef8af4e5557fd</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>GenAI Python Systems Engineer – Senior Associate</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>10</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Data Lake, Docker, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d341008fd89dae92</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>GenAI Python Systems Engineer – Senior Associate</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>10</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Data Lake, Docker, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=229cba137d57807d</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>GenAI Python Systems Engineer – Senior Associate</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Des Moines, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>10</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Data Lake, Docker, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1beeee280545a4d8</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>GenAI Python Systems Engineer – Senior Associate</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>10</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Data Lake, Docker, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d7c5fa3bce450556</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>GenAI Python Systems Engineer – Senior Associate</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Grand Rapids, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>10</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Data Lake, Docker, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=39294e745bb0f76e</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>GenAI Python Systems Engineer – Senior Associate</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>10</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Data Lake, Docker, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=099eae4c40f6e37a</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>GenAI Python Systems Engineer – Senior Associate</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>10</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Data Lake, Docker, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8b3487536b109ec4</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>GenAI Python Systems Engineer – Senior Associate</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>10</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Data Lake, Docker, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bf8e9b8c0b8558b5</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>GenAI Python Systems Engineer – Senior Associate</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>10</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Data Lake, Docker, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bc69adc96717a25b</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>GenAI Python Systems Engineer – Senior Associate</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Jacksonville, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>10</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Data Lake, Docker, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d06666a52e7fc592</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>GenAI Python Systems Engineer – Senior Associate</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>10</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Data Lake, Docker, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9ecda4cdbf490425</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>GenAI Python Systems Engineer – Senior Associate</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>10</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Data Lake, Docker, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f0a2dcd15f470402</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>GenAI Python Systems Engineer – Senior Associate</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>10</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Data Lake, Docker, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b6327e7fe9d7e389</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>GenAI Python Systems Engineer – Senior Associate</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>San Antonio, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>10</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Data Lake, Docker, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=74ba52ae4f8a2948</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>GenAI Python Systems Engineer – Senior Associate</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Silicon Valley, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>10</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Data Lake, Docker, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fbc65af7ca7077af</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>GenAI Python Systems Engineer – Senior Associate</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Oklahoma City, OK, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>10</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Data Lake, Docker, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=34c7afec89e4cb86</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>GenAI Python Systems Engineer – Senior Associate</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Tulsa, OK, US USA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>10</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Data Lake, Docker, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6b8ababc6fedb2ad</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>GenAI Python Systems Engineer – Senior Associate</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Louisville, KY, US USA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>10</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Data Lake, Docker, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=288f1b14b9bb2946</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>GenAI Python Systems Engineer – Senior Associate</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>10</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Data Lake, Docker, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d18340c211b5a5bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>GenAI Python Systems Engineer – Senior Associate</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Rosemont, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>10</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Data Lake, Docker, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3116efa3360df29b</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>GenAI Python Systems Engineer – Senior Associate</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Salt Lake City, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>10</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Data Lake, Docker, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dd8868954104ab1a</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>GenAI Python Systems Engineer – Senior Associate</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Sacramento, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>10</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Data Lake, Docker, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=021a87e205105721</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>GenAI Python Systems Engineer – Senior Associate</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Columbia, SC, US USA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>10</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Data Lake, Docker, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1324ebe201b47273</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>GenAI Python Systems Engineer – Senior Associate</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>10</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Data Lake, Docker, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6d8031393f02e75e</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>GenAI Python Systems Engineer – Senior Associate</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>10</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Data Lake, Docker, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=267faf1cf944de29</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>GenAI Python Systems Engineer – Senior Associate</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Cincinnati, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>10</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Data Lake, Docker, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9920f2d7a66255a2</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>GenAI Python Systems Engineer – Senior Associate</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>New Orleans, LA, US USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>10</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Data Lake, Docker, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=53b67630c6031bfc</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>GenAI Python Systems Engineer – Senior Associate</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Buffalo, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>10</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Data Lake, Docker, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=19ee213f40ffe54c</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>GenAI Python Systems Engineer – Senior Associate</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Toledo, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>10</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Data Lake, Docker, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=79c4f92ed2837ac5</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>GenAI Python Systems Engineer – Senior Associate</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>10</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Data Lake, Docker, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1524086009e62a0f</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>GenAI Python Systems Engineer – Senior Associate</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Milwaukee, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>10</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Data Lake, Docker, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=836957d4e3d33df1</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>GenAI Python Systems Engineer – Senior Associate</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Greensboro, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>10</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Data Lake, Docker, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6aa08ddbf345b08f</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>GenAI Python Systems Engineer – Senior Associate</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Cleveland, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>10</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Data Lake, Docker, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=32bfc34ec0227321</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>GenAI Python Systems Engineer – Senior Associate</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>10</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Data Lake, Docker, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c27f63fd3045d980</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>GenAI Python Systems Engineer – Senior Associate</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>10</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Data Lake, Docker, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0c9dbc57cdeef363</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>GenAI Python Systems Engineer – Senior Associate</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Fort Worth, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>10</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Data Lake, Docker, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=22ae5eff4ade28e9</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>GenAI Python Systems Engineer – Senior Associate</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>10</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Data Lake, Docker, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cdcdad718d96daf2</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>GenAI Python Systems Engineer – Senior Associate</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>10</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Data Lake, Docker, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6d29995435c8e01c</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>GenAI Python Systems Engineer – Senior Associate</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>10</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Data Lake, Docker, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f1de2e5b6c4e8454</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>GenAI Python Systems Engineer – Senior Associate</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>10</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Data Lake, Docker, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9dbf8d7f23ad6f59</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>GenAI Python Systems Engineer – Senior Associate</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Albany, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>10</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Data Lake, Docker, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bb1832eaee344341</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>GenAI Python Systems Engineer – Senior Associate</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>10</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Data Lake, Docker, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9ce1b38552a00163</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>GenAI Python Systems Engineer – Senior Associate</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Baltimore, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>10</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Data Lake, Docker, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0d51ebec341742b3</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>GenAI Python Systems Engineer – Senior Associate</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Stamford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>10</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Data Lake, Docker, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1e0e31c997112ecb</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer – Full Stack</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>10</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5f4cb6c46f58f623</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer – Full Stack</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>10</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=957d0ddcede82e51</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer – Full Stack</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>10</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9ae973243ac5d4d3</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer – Full Stack</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>10</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ac399ba01940b3ea</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer – Full Stack</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>10</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e6640e136af1cb10</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer – Full Stack</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>10</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d6113d33d84562ec</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer – Full Stack</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>10</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ff0ae847d39bf95f</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer – Full Stack</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Fort Lauderdale, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>10</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2cb18569154c4f78</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer – Full Stack</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Louisville, KY, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>10</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4d4620045731c558</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer – Full Stack</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>10</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=07f9536f10547f6d</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer – Full Stack</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>NY, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>10</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5e24f3c7fd05843c</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer – Full Stack</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Fort Lauderdale, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>10</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f663ce546826dc53</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>AI Native Software Engineer</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>10</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=31565d669802996c</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>AI &amp; Data Analytics Co-op/Intern</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>AMOT Controls</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>10</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, Prompt Engineering, Git, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aa36c8dc5013838e</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-05-08.xlsx
+++ b/daily_matches/job_matches_2026-05-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Junior Generative AI Application Developer</t>
+          <t>Kubernetes Cloud Engineer (EKS)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Citi</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>27.8</v>
+        <v>25.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Copilot, Hugging Face, Prompt Engineering, TensorFlow</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, Copilot, FAISS, Pinecone, Prompt Engineering, S3, EC2</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0a243477a745eb9</t>
+          <t>https://www.indeed.com/viewjob?jk=0c4556ba273a002c</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Junior Generative AI Application Developer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Citi</t>
+          <t>Cadrac Labs India Private Limited</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Texas City, IL, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>27.8</v>
+        <v>21.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Copilot, Hugging Face, Prompt Engineering, TensorFlow</t>
+          <t>Data Scientist, Generative AI, Data Lake, Docker, Kubernetes, CI/CD, Git, Snowflake, Databricks, Kafka</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=874f5ca1092189ef</t>
+          <t>https://www.indeed.com/viewjob?jk=747aafe9f6bd6536</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Junior Generative AI Application Developer</t>
+          <t>Senior DevOps Engineer (Kubernetes)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Citi</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>27.8</v>
+        <v>21.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Copilot, Hugging Face, Prompt Engineering, TensorFlow</t>
+          <t>Generative AI, RAG, Gemini, Copilot, BigQuery, Docker, Kubernetes, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce3d565040e4deeb</t>
+          <t>https://www.indeed.com/viewjob?jk=381d7c89737513ad</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Junior Generative AI Application Developer</t>
+          <t>Data Scientist – Transmission ROW Risk Analytics</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Citi</t>
+          <t>GSR Business Services</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Dublin, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>27.8</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Copilot, Hugging Face, Prompt Engineering, TensorFlow</t>
+          <t>Data Scientist, RAG, TensorFlow, Hadoop, Tableau, Power BI, Matplotlib, Seaborn, Python, SQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d09fccd840d1ac8</t>
+          <t>https://www.indeed.com/viewjob?jk=29f5653468bdf4f8</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Associate - Data Scientist</t>
+          <t>Generative AI Intern</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,69 +626,69 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, CI/CD, Git, Snowflake, Databricks, Python, SQL</t>
+          <t>Generative AI, RAG, BigQuery, FastAPI, Docker, CI/CD, Terraform, BigQuery, PySpark, Hadoop</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c97444142366cb8a</t>
+          <t>https://www.indeed.com/viewjob?jk=5be60fbee58aedc1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Applied Scientist [Short Term Assignment] - FuzeRx</t>
+          <t>Senior Data Engineer - APIs</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Fuze Health</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, Hugging Face, TensorFlow, PyTorch, Git, Python, SQL</t>
+          <t>RAG, BigQuery, Dataflow, Kubernetes, CI/CD, Git, BigQuery, Kafka, Python, SQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51cb583ceb58a94a</t>
+          <t>https://www.indeed.com/viewjob?jk=ecb5dd3a0318428a</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Applied Scientist - FuzeRx</t>
+          <t>Software Development Engineer in Test, ML</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Fuze Health</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,34 +696,34 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, Hugging Face, TensorFlow, PyTorch, Git, Python, SQL</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed081979bb6e73b0</t>
+          <t>https://www.indeed.com/viewjob?jk=03cd36eaa85418b7</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Azure)</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Blue Sentry Cloud</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Glue, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, NoSQL, SQL, R</t>
+          <t>Generative AI, RAG, EC2, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8b2646dabbd2b10</t>
+          <t>https://www.indeed.com/viewjob?jk=6a6b3824199c4c56</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>AI/ML Platform Architect</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ShyftOff</t>
+          <t>Hiring Street</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>East Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, EC2, FastAPI, Git, PostgreSQL, SQL, R, Scala</t>
+          <t>Data Scientist, RAG, Prompt Engineering, TensorFlow, Azure ML, MLflow, Docker, Kubernetes, CI/CD, Databricks</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=424966b154b3ad42</t>
+          <t>https://www.indeed.com/viewjob?jk=df314297aa2f0f35</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AI Analyst - Finance Technology</t>
+          <t>Sr Software Development Engineer in Test, ML</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Victaulic</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Easton, PA, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Prompt Engineering, Cortex, Snowflake, Python, SQL, R, Optimization</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a75432ccfb7c7783</t>
+          <t>https://www.indeed.com/viewjob?jk=d9632e09bbc8fbcf</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AI Analyst - Finance Technology</t>
+          <t>Senior Platform Engineer (Azure)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Victaulic</t>
+          <t>Blue Sentry Cloud</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Prompt Engineering, Cortex, Snowflake, Python, SQL, R, Optimization</t>
+          <t>Glue, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, NoSQL, SQL, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43f314bf05e91473</t>
+          <t>https://www.indeed.com/viewjob?jk=0ad9db5da19a8799</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Associate, Software Engineer</t>
+          <t>Software Engineering Intern, DataOps Engineering / Data Engineering</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>Luminate</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Jenkins, Git, Kafka, SQL, R, Java</t>
+          <t>Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d67482930db7e10</t>
+          <t>https://www.indeed.com/viewjob?jk=c0e13b4073216a84</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Scientist II</t>
+          <t>Software Engineer - Core Product</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Vectra AI</t>
+          <t>PagerDuty</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Git, NoSQL, Python, SQL, R, Java, Scala</t>
+          <t>Generative AI, RAG, Git, Kafka, MySQL, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,42 +916,497 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=225195d492596ed1</t>
+          <t>https://www.indeed.com/viewjob?jk=d4b8d50d4bd3428e</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Fresher - NLP Engineer</t>
+          <t>Cloud Operations Associate (GCP)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Busigence Technologies</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>S3, Docker, Kubernetes, AKS, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0b1c67caa8dada84</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Associate Cloud Security Analyst</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>S3, Docker, Kubernetes, AKS, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eae5a2d66b2f3420</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Junior Kubernetes Engineer</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>S3, Docker, Kubernetes, AKS, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1272708dac2e408f</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Agentic AI Engineer - USC and Green Card Holders || W2 Role</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Hudson Manpower</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LangChain, Hugging Face, FAISS, Pinecone, Prompt Engineering, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a87b6afa96a2f0bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Machine Learning Intern</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>CI/CD, Snowflake, Kafka, PostgreSQL, Power BI, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ca7c2d316ed79d27</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Generative AI Intern</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, Kubernetes, CI/CD, Jenkins, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5d6cf6f520e6fbe7</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Data Scientist - DCCA</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Board of Governors of the Federal Reserve System</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, Tableau, Power BI, Matplotlib, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b64766f37995a5bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Sr. Product Specialist, Analytics &amp; Machine Learning</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Northern Trust Corp.</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Snowflake, Databricks, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cc251560c46e69ed</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Forward Deployment Engineer - AI &amp; Agentic Solutions</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Visionary Integration Professionals</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
           <t>Remote, US USA</t>
         </is>
       </c>
-      <c r="D15" t="n">
+      <c r="D23" t="n">
         <v>10</v>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>NLP Engineer, TensorFlow, PyTorch, Keras, spaCy, NLTK, Gensim, Python, R</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2022-07-30</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=389d24774bf5a0ba</t>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Gemini, Copilot, Prompt Engineering, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=63199d50fb2b5826</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Kubernetes CI/CD Engineer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Terraform, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0d96f3adde2aba5a</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>AWS API Engineer</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>10</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, FastAPI, CI/CD, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1a6d18fc9f4997d7</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>AWS API Engineer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>10</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RAG, S3, EC2, Terraform, Kafka, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e17e515a278179f0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Intern</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>EXL Service</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>10</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Data Scientist, Git, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=95f9784006f8388a</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>AI Intern</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>10</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Data Scientist, LangChain, RAG, Prompt Engineering, BigQuery, BigQuery, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=360828a46dfc06c8</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-05-08.xlsx
+++ b/daily_matches/job_matches_2026-05-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Kubernetes Cloud Engineer (EKS)</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>25.6</v>
+        <v>20</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Copilot, FAISS, Pinecone, Prompt Engineering, S3, EC2</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Hugging Face, TensorFlow, PyTorch, Keras, FastAPI, Docker</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c4556ba273a002c</t>
+          <t>https://www.indeed.com/viewjob?jk=dbb39d1d14efd21d</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Cadrac Labs India Private Limited</t>
+          <t>Sonar</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Texas City, IL, US USA</t>
+          <t>Chattanooga, TN, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>21.1</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, Data Lake, Docker, Kubernetes, CI/CD, Git, Snowflake, Databricks, Kafka</t>
+          <t>RAG, S3, BigQuery, Dataflow, FastAPI, Kubernetes, Apache Airflow, Terraform, BigQuery, MySQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=747aafe9f6bd6536</t>
+          <t>https://www.indeed.com/viewjob?jk=09ccfeeca461865f</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (Kubernetes)</t>
+          <t>Senior DevOps / Platform Reliability Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Zingtree</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>21.1</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Copilot, BigQuery, Docker, Kubernetes, CI/CD, Terraform, Git</t>
+          <t>Copilot, S3, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=381d7c89737513ad</t>
+          <t>https://www.indeed.com/viewjob?jk=63a7e7b3bf60f979</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Scientist – Transmission ROW Risk Analytics</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>GSR Business Services</t>
+          <t>Inovalon</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dublin, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, Hadoop, Tableau, Power BI, Matplotlib, Seaborn, Python, SQL</t>
+          <t>Machine Learning Engineer, Generative AI, RAG, Copilot, PyTorch, Docker, Kubernetes, Git, NoSQL, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29f5653468bdf4f8</t>
+          <t>https://www.indeed.com/viewjob?jk=2aa9fcbe794b8aa2</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Generative AI Intern</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nCino</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, BigQuery, FastAPI, Docker, CI/CD, Terraform, BigQuery, PySpark, Hadoop</t>
+          <t>Data Scientist, RAG, S3, Athena, MLflow, Databricks, NoSQL, Tableau, Quicksight, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5be60fbee58aedc1</t>
+          <t>https://www.indeed.com/viewjob?jk=c2c0d4d0938bf55c</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - APIs</t>
+          <t>Software Development Engineer in Test, ML</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Dataflow, Kubernetes, CI/CD, Git, BigQuery, Kafka, Python, SQL</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecb5dd3a0318428a</t>
+          <t>https://www.indeed.com/viewjob?jk=50a9750053034f93</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test, ML</t>
+          <t>UX Software Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Charles River Analytics</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R</t>
+          <t>S3, EC2, Docker, Kubernetes, Git, MySQL, MongoDB, Python, SQL, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03cd36eaa85418b7</t>
+          <t>https://www.indeed.com/viewjob?jk=5392f87fadaec778</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>Sr Software Development Engineer in Test, ML</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, EC2, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a6b3824199c4c56</t>
+          <t>https://www.indeed.com/viewjob?jk=65fb9eb3f94c2fcb</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AI/ML Platform Architect</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Hiring Street</t>
+          <t>ＡＮＧＥＬ</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>East Newark, NJ, US USA</t>
+          <t>Provo, UT, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Prompt Engineering, TensorFlow, Azure ML, MLflow, Docker, Kubernetes, CI/CD, Databricks</t>
+          <t>Data Scientist, RAG, Redshift, BigQuery, Snowflake, BigQuery, Redshift, Python, SQL, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df314297aa2f0f35</t>
+          <t>https://www.indeed.com/viewjob?jk=cd49260a506eada7</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr Software Development Engineer in Test, ML</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>NorthMarq</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Golden Valley, MN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R</t>
+          <t>RAG, Cortex, CI/CD, Git, Snowflake, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9632e09bbc8fbcf</t>
+          <t>https://www.indeed.com/viewjob?jk=c75e31192e70f299</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Azure)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Blue Sentry Cloud</t>
+          <t>NorthMarq</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Glue, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, NoSQL, SQL, R</t>
+          <t>RAG, Cortex, CI/CD, Git, Snowflake, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ad9db5da19a8799</t>
+          <t>https://www.indeed.com/viewjob?jk=3378ba0a224291a9</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Engineering Intern, DataOps Engineering / Data Engineering</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Luminate</t>
+          <t>NorthMarq</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Burnsville, MN, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Python, SQL, R, Java</t>
+          <t>RAG, Cortex, CI/CD, Git, Snowflake, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0e13b4073216a84</t>
+          <t>https://www.indeed.com/viewjob?jk=3454b8bb44e492ea</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Engineer - Core Product</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PagerDuty</t>
+          <t>NorthMarq</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Git, Kafka, MySQL, NoSQL, Python, SQL, R, Java</t>
+          <t>RAG, Cortex, CI/CD, Git, Snowflake, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4b8d50d4bd3428e</t>
+          <t>https://www.indeed.com/viewjob?jk=30f4be82e636b033</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Cloud Operations Associate (GCP)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NorthMarq</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>S3, Docker, Kubernetes, AKS, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>RAG, Cortex, CI/CD, Git, Snowflake, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b1c67caa8dada84</t>
+          <t>https://www.indeed.com/viewjob?jk=61284841e88348e1</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Associate Cloud Security Analyst</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NorthMarq</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Richfield, MN, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>S3, Docker, Kubernetes, AKS, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>RAG, Cortex, CI/CD, Git, Snowflake, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eae5a2d66b2f3420</t>
+          <t>https://www.indeed.com/viewjob?jk=f03781722277716e</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Junior Kubernetes Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NorthMarq</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>S3, Docker, Kubernetes, AKS, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>RAG, Cortex, CI/CD, Git, Snowflake, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1272708dac2e408f</t>
+          <t>https://www.indeed.com/viewjob?jk=0a4e8b14af6dcfdc</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Agentic AI Engineer - USC and Green Card Holders || W2 Role</t>
+          <t>2026-2027 Information Technology – Information and Analytics – Intern</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Hudson Manpower</t>
+          <t>Chevron</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, Hugging Face, FAISS, Pinecone, Prompt Engineering, Python, R, Scala</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, Data Lake, CI/CD, Git, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a87b6afa96a2f0bb</t>
+          <t>https://www.indeed.com/viewjob?jk=d850ce0ad808b039</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Machine Learning Intern</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>DocMe360</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CI/CD, Snowflake, Kafka, PostgreSQL, Power BI, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Copilot, Docker, CI/CD, Git, NoSQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca7c2d316ed79d27</t>
+          <t>https://www.indeed.com/viewjob?jk=10188be426c573fc</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Generative AI Intern</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>DAT Solutions</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, Kubernetes, CI/CD, Jenkins, Python, R, Java</t>
+          <t>LangChain, RAG, Docker, Kubernetes, Terraform, Kafka, PostgreSQL, MongoDB, SQL, R</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d6cf6f520e6fbe7</t>
+          <t>https://www.indeed.com/viewjob?jk=d6127d24941f5ff7</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Scientist - DCCA</t>
+          <t>(2) AI Developers (Software Development Specialist 1)- 20066914, 20066924</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Board of Governors of the Federal Reserve System</t>
+          <t>State of Ohio</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, Tableau, Power BI, Matplotlib, Python, SQL, R</t>
+          <t>RAG, Copilot, PyTorch, AKS, Git, Snowflake, Matplotlib, Seaborn, Python, SQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b64766f37995a5bb</t>
+          <t>https://www.indeed.com/viewjob?jk=31021337eb001bb4</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr. Product Specialist, Analytics &amp; Machine Learning</t>
+          <t>Generative AI Engineer (Specialist - Data Sciences)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Northern Trust Corp.</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, Snowflake, Databricks, Power BI, Python, SQL, R, Scala</t>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, LLaMA, Prompt Engineering, TensorFlow, PyTorch, Python, R</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc251560c46e69ed</t>
+          <t>https://www.indeed.com/viewjob?jk=bf5c7964770fdb4c</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Forward Deployment Engineer - AI &amp; Agentic Solutions</t>
+          <t>Systems Architect - Infrastructure</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Visionary Integration Professionals</t>
+          <t>Analytica</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Gemini, Copilot, Prompt Engineering, Git, Python, R, Java</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Databricks, Hadoop, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63199d50fb2b5826</t>
+          <t>https://www.indeed.com/viewjob?jk=fb04e93fa894fc64</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Kubernetes CI/CD Engineer</t>
+          <t>Business Data Scientist</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Syracuse University</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Syracuse, NY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Terraform, Python, R, Scala</t>
+          <t>Data Scientist, RAG, XGBoost, Tableau, Power BI, Python, SQL, R, Scala, A/B Testing</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d96f3adde2aba5a</t>
+          <t>https://www.indeed.com/viewjob?jk=5f59a96056ee48af</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AWS API Engineer</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RAG, Copilot, FastAPI, CI/CD, NoSQL, Python, SQL, R, Scala</t>
+          <t>AI Engineer, Data Scientist, RAG, CI/CD, Python, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a6d18fc9f4997d7</t>
+          <t>https://www.indeed.com/viewjob?jk=462d0505f646c5b1</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AWS API Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Navan</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Terraform, Kafka, Python, SQL, R, Java</t>
+          <t>RAG, Gemini, CI/CD, Jenkins, Terraform, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e17e515a278179f0</t>
+          <t>https://www.indeed.com/viewjob?jk=f67d8d029604a63e</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Senior Software Engineer, AI</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Plains Marketing</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Data Scientist, Git, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, Copilot, Data Lake, Databricks, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95f9784006f8388a</t>
+          <t>https://www.indeed.com/viewjob?jk=77de500690be1561</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AI Intern</t>
+          <t>IT AI System Administrator - AI Offerings</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Lenovo</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, Prompt Engineering, BigQuery, BigQuery, Python, SQL, R</t>
+          <t>AI Engineer, RAG, Docker, Kubernetes, CI/CD, Terraform, Python, R, Scala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,7 +1406,147 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=360828a46dfc06c8</t>
+          <t>https://www.indeed.com/viewjob?jk=7a8474a0197ab9dc</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Senior Go Software Engineer</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Array</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Docker, Kubernetes, Git, MongoDB, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7e36fedf9d7697b7</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>10</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, Pinecone, CI/CD, GitHub Actions, Git, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f242f09dbc0e1b1c</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst - 2363198</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>MN, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>10</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>RAG, Jenkins, Git, Python, SQL, R, Java, Scala, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b025f0768ba98576</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>ENIN SYSTEMS</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>10</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=45585f8419e6b1c0</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-05-08.xlsx
+++ b/daily_matches/job_matches_2026-05-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Data Engineer I or II</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Southern Company</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>31.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Hugging Face, TensorFlow, PyTorch, Keras, FastAPI, Docker</t>
+          <t>Data Scientist, S3, Redshift, BigQuery, Data Lake, Dataflow, Docker, Kubernetes, Apache Airflow, CI/CD</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbb39d1d14efd21d</t>
+          <t>https://www.indeed.com/viewjob?jk=432940e5c429b71c</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer I or II</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Sonar</t>
+          <t>Southern Company</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Chattanooga, TN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>31.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, S3, BigQuery, Dataflow, FastAPI, Kubernetes, Apache Airflow, Terraform, BigQuery, MySQL</t>
+          <t>Data Scientist, S3, Redshift, BigQuery, Data Lake, Dataflow, Docker, Kubernetes, Apache Airflow, CI/CD</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09ccfeeca461865f</t>
+          <t>https://www.indeed.com/viewjob?jk=94efcb73c0d62620</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior DevOps / Platform Reliability Engineer</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Zingtree</t>
+          <t>Hinge</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>20</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Copilot, S3, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Kafka, MySQL</t>
+          <t>RAG, Redshift, BigQuery, Dataflow, Docker, Kubernetes, GitHub Actions, Terraform, Git, Databricks</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63a7e7b3bf60f979</t>
+          <t>https://www.indeed.com/viewjob?jk=8f8363856d6fd5ea</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>GCP Data Architect with 15 year's experience local to Chicago</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Inovalon</t>
+          <t>Sanford AI</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>18.9</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, Copilot, PyTorch, Docker, Kubernetes, Git, NoSQL, Python</t>
+          <t>RAG, BigQuery, Data Lake, Dataflow, CI/CD, Terraform, Git, Snowflake, Databricks, BigQuery</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2aa9fcbe794b8aa2</t>
+          <t>https://www.indeed.com/viewjob?jk=fcb6ec77e71bc3c8</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>nCino</t>
+          <t>Ascendion</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>18.9</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, Athena, MLflow, Databricks, NoSQL, Tableau, Quicksight, Python</t>
+          <t>LangChain, RAG, S3, Glue, Redshift, Apache Airflow, Git, Snowflake, Databricks, Redshift</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2c0d4d0938bf55c</t>
+          <t>https://www.indeed.com/viewjob?jk=f03c0c824aa43ad2</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test, ML</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>18.9</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R</t>
+          <t>S3, Glue, Redshift, Data Lake, Kinesis, CI/CD, Terraform, Snowflake, Databricks, Redshift</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50a9750053034f93</t>
+          <t>https://www.indeed.com/viewjob?jk=f631622e574168df</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>UX Software Engineer</t>
+          <t>Java AWS Developer (8 or Above yrs of experienced professionals)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Charles River Analytics</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>17.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>S3, EC2, Docker, Kubernetes, Git, MySQL, MongoDB, Python, SQL, R</t>
+          <t>Generative AI, RAG, Gemini, Kinesis, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5392f87fadaec778</t>
+          <t>https://www.indeed.com/viewjob?jk=5114b2dc892b00c6</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr Software Development Engineer in Test, ML</t>
+          <t>GCP Cloud Architect</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R</t>
+          <t>Generative AI, RAG, Gemini, BigQuery, Dataflow, Kubernetes, CI/CD, Jenkins, Terraform, Git</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,102 +741,102 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65fb9eb3f94c2fcb</t>
+          <t>https://www.indeed.com/viewjob?jk=3d9a604036ab5e2b</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior AWS Developer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ＡＮＧＥＬ</t>
+          <t>Altumint</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Provo, UT, US USA</t>
+          <t>Lanham, MD, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Redshift, BigQuery, Snowflake, BigQuery, Redshift, Python, SQL, R</t>
+          <t>S3, EC2, Docker, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, MySQL, Python</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd49260a506eada7</t>
+          <t>https://www.indeed.com/viewjob?jk=fed653aec24910be</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Full-Stack Engineer (Python &amp; React)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NorthMarq</t>
+          <t>Factored</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Golden Valley, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Cortex, CI/CD, Git, Snowflake, Power BI, Python, SQL, R, Scala</t>
+          <t>Generative AI, RAG, Gemini, FastAPI, CI/CD, Git, PostgreSQL, MySQL, NoSQL, Python</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c75e31192e70f299</t>
+          <t>https://www.indeed.com/viewjob?jk=724d0d8443bffbcf</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>SRE/DevOps Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NorthMarq</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Cortex, CI/CD, Git, Snowflake, Power BI, Python, SQL, R, Scala</t>
+          <t>Generative AI, RAG, Gemini, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3378ba0a224291a9</t>
+          <t>https://www.indeed.com/viewjob?jk=64be9beb3d73dbb9</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NorthMarq</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Burnsville, MN, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Cortex, CI/CD, Git, Snowflake, Power BI, Python, SQL, R, Scala</t>
+          <t>Pinecone, BigQuery, MLflow, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, BigQuery</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3454b8bb44e492ea</t>
+          <t>https://www.indeed.com/viewjob?jk=58f2445240dbd78a</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>NorthMarq</t>
+          <t>Health in Tech</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Cortex, CI/CD, Git, Snowflake, Power BI, Python, SQL, R, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, PostgreSQL, MySQL, MongoDB, NoSQL, Python</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30f4be82e636b033</t>
+          <t>https://www.indeed.com/viewjob?jk=3f5057bd977bc6a4</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>GenAI/Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>NorthMarq</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Cortex, CI/CD, Git, Snowflake, Power BI, Python, SQL, R, Scala</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Prompt Engineering, Git, Databricks, Python</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61284841e88348e1</t>
+          <t>https://www.indeed.com/viewjob?jk=f094c43b2df8d8a8</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Data Engineering Consultant - Remote</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>NorthMarq</t>
+          <t>UnitedHealthcare</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Richfield, MN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Cortex, CI/CD, Git, Snowflake, Power BI, Python, SQL, R, Scala</t>
+          <t>Redshift, CI/CD, Git, Snowflake, Databricks, Redshift, Kafka, Python, SQL, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f03781722277716e</t>
+          <t>https://www.indeed.com/viewjob?jk=5d70310be183ea2e</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Gen AI/ML Data Scientist</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>NorthMarq</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Cortex, CI/CD, Git, Snowflake, Power BI, Python, SQL, R, Scala</t>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Gemini, Docker, CI/CD, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a4e8b14af6dcfdc</t>
+          <t>https://www.indeed.com/viewjob?jk=280501a562f0fb78</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-2027 Information Technology – Information and Analytics – Intern</t>
+          <t>Senior Platform Engineer (Cloud Platform)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Chevron</t>
+          <t>Amplitude</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, Data Lake, CI/CD, Git, Python, SQL, R, Scala</t>
+          <t>RAG, S3, EC2, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d850ce0ad808b039</t>
+          <t>https://www.indeed.com/viewjob?jk=6e26c106f1b8164f</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DocMe360</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, CI/CD, Git, NoSQL, SQL, R, Java, Scala</t>
+          <t>Generative AI, RAG, Gemini, BigQuery, Dataflow, CI/CD, Git, BigQuery, Python, R</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10188be426c573fc</t>
+          <t>https://www.indeed.com/viewjob?jk=7a52c33ac5a346e1</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>DAT Solutions</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Docker, Kubernetes, Terraform, Kafka, PostgreSQL, MongoDB, SQL, R</t>
+          <t>Generative AI, RAG, Gemini, CI/CD, Git, Databricks, Tableau, Power BI, SQL, R</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6127d24941f5ff7</t>
+          <t>https://www.indeed.com/viewjob?jk=17624144d4bde746</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>(2) AI Developers (Software Development Specialist 1)- 20066914, 20066924</t>
+          <t>Senior Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>State of Ohio</t>
+          <t>Dragonfli Group LLC</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, Copilot, PyTorch, AKS, Git, Snowflake, Matplotlib, Seaborn, Python, SQL</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Terraform, Git, Databricks, PySpark, Python</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31021337eb001bb4</t>
+          <t>https://www.indeed.com/viewjob?jk=b51c0221c27e18ee</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Generative AI Engineer (Specialist - Data Sciences)</t>
+          <t>Senior Artificial Intelligence Software Engineer (Hybrid Eligible)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Oak Ridge National Laboratory</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Oak Ridge, TN, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, LLaMA, Prompt Engineering, TensorFlow, PyTorch, Python, R</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, Copilot, Hugging Face, TensorFlow, PyTorch, CI/CD, Python</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf5c7964770fdb4c</t>
+          <t>https://www.indeed.com/viewjob?jk=1fe1061f779eda0d</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Systems Architect - Infrastructure</t>
+          <t>Machine Learning Engineer, Trust &amp; Safety</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Analytica</t>
+          <t>Hinge</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Databricks, Hadoop, R, Scala, Optimization</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, Hugging Face, PyTorch, Kubernetes, Git, Databricks, Python, SQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb04e93fa894fc64</t>
+          <t>https://www.indeed.com/viewjob?jk=b249efe72c30be08</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Business Data Scientist</t>
+          <t>Data Scientist - Commercial Analytics</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Syracuse University</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Syracuse, NY, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, XGBoost, Tableau, Power BI, Python, SQL, R, Scala, A/B Testing</t>
+          <t>Data Scientist, XGBoost, LightGBM, CI/CD, Snowflake, Databricks, PySpark, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f59a96056ee48af</t>
+          <t>https://www.indeed.com/viewjob?jk=a183d21d1bc32a73</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Associate Data Scientist – Finance &amp; Accounting Automation</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, CI/CD, Python, R, Java, Scala, Optimization</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, TensorFlow, PyTorch, Redshift, Redshift, Tableau, Power BI</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=462d0505f646c5b1</t>
+          <t>https://www.indeed.com/viewjob?jk=d317baacdb2ac3fa</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Python Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Navan</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RAG, Gemini, CI/CD, Jenkins, Terraform, Python, R, Java, Scala</t>
+          <t>Generative AI, RAG, Gemini, BigQuery, Git, BigQuery, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f67d8d029604a63e</t>
+          <t>https://www.indeed.com/viewjob?jk=916b0eb9ca93a7a2</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, AI</t>
+          <t>Data Migration Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Plains Marketing</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Data Lake, Databricks, Python, SQL, R, Scala, Optimization</t>
+          <t>Generative AI, RAG, Gemini, Git, Snowflake, Kafka, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77de500690be1561</t>
+          <t>https://www.indeed.com/viewjob?jk=9f01b1849bd3f7de</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>IT AI System Administrator - AI Offerings</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Lenovo</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Docker, Kubernetes, CI/CD, Terraform, Python, R, Scala</t>
+          <t>RAG, CI/CD, Git, Databricks, PySpark, Tableau, Power BI, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a8474a0197ab9dc</t>
+          <t>https://www.indeed.com/viewjob?jk=794fd3442926e801</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Go Software Engineer</t>
+          <t>Data Migration Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Array</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Docker, Kubernetes, Git, MongoDB, SQL, R, Java</t>
+          <t>Generative AI, RAG, Gemini, Git, Snowflake, Kafka, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e36fedf9d7697b7</t>
+          <t>https://www.indeed.com/viewjob?jk=df00417b3da3f42f</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Migration Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Pinecone, CI/CD, GitHub Actions, Git, R, Scala, Optimization</t>
+          <t>Generative AI, RAG, Gemini, Git, Snowflake, Kafka, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f242f09dbc0e1b1c</t>
+          <t>https://www.indeed.com/viewjob?jk=24d8dcba808e253f</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Analyst - 2363198</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>DRAGOS</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RAG, Jenkins, Git, Python, SQL, R, Java, Scala, A/B Testing</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, NoSQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,42 +1511,847 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b025f0768ba98576</t>
+          <t>https://www.indeed.com/viewjob?jk=b7048d55ba34c919</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>Senior QA Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=29931ba9e2678a00</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Research Assistant</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>University of North Texas</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Denton, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, XGBoost, Keras, MLflow, FastAPI, Docker, Git, Python</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=449f9b695d435059</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>MLOps Data Engineer</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, MLflow, Kubernetes, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=34fcacb2f302dc22</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Azure Databricks Engineer</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, Synapse, Git, Databricks, PySpark, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8c94f00b22e57d86</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Amplitude</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Git, Hadoop, Python, SQL, R, Optimization, Bayesian, Hypothesis Testing</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a44bb3451757db0b</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Amplitude</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>RAG, S3, Kubernetes, Terraform, Git, Snowflake, Kafka, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d573a1a4fd376e26</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Adobe Commerce Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Asset Marketing Services</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Eagan, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Git, MySQL, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=16a89d83a06c5742</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Akkadian Labs</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Hoboken, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=56e78fa05eac6e15</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Software Engineer, (L2) CDP</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Twilio</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, Kafka, PostgreSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=38ff081155f4529b</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Clearlink</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Draper, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Data Lake, Git, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7fcc1c840bd1c22a</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer (Chicago, Atlanta, Boston)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>8th Light</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, CI/CD, Git, Databricks, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=23a94ad39c7ec6bf</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>IT Data Science Engineer</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>SubCom</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Newington, NH, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Synapse, Data Lake, CI/CD, Git, Power BI, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c70b005bd5571ce9</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Junior Python Engineer</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Altumint</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Lanham, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>FastAPI, Docker, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=56bf68959ce66852</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>SCADA Engineer</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>10</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, Git, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=43926177b43175c1</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Referral Only- GCP Solution Architect</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>10</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, Kubernetes, CI/CD, Terraform, Git, R, Scala</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=73fabb58ae40bd7f</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>SDET (POS Automation)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Bellevue, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>10</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=31ac04dd37bf808a</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Embedded Software Developer for RDK-B</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Santa Clara, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>10</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, Docker, CI/CD, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8da5199081e49bcd</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Engineer</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>10</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>CI/CD, MongoDB, NoSQL, Python, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ee77fd9889843e4c</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Senior Research Engineer - Voleon Securities</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>The Voleon Group</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Berkeley, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>10</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>RAG, PyTorch, MySQL, MongoDB, Cassandra, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a24e5d5893a94fec</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Senior Research Engineer - Voleon Securities</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>The Voleon Group</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>10</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>RAG, PyTorch, MySQL, MongoDB, Cassandra, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=06c817f70e864a3d</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Vendelux</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>10</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e3bd484668de1f94</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Vendelux</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>10</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ed3ae1a38cca1ea2</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Fire &amp; Police Pension Association</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>10</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, AKS, CI/CD, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=81e9dbcfe4537ee6</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
           <t>Data Scientist</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>ENIN SYSTEMS</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Zoom Communications</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
         <v>10</v>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=45585f8419e6b1c0</t>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, MLflow, Snowflake, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f4f7bb7f6cc5ed4e</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-05-08.xlsx
+++ b/daily_matches/job_matches_2026-05-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G55"/>
+  <dimension ref="A1:G76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer I or II</t>
+          <t>Data Scientist with Python expertise in New York</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Southern Company</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>31.1</v>
+        <v>20</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, S3, Redshift, BigQuery, Data Lake, Dataflow, Docker, Kubernetes, Apache Airflow, CI/CD</t>
+          <t>Data Scientist, Generative AI, RAG, Gemini, XGBoost, LightGBM, Redshift, BigQuery, MLflow, Git</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,19 +496,19 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=432940e5c429b71c</t>
+          <t>https://www.indeed.com/viewjob?jk=7da54b6ae0f47c98</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer I or II</t>
+          <t>AWS Data Scientist</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Southern Company</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -517,11 +517,11 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>31.1</v>
+        <v>20</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, S3, Redshift, BigQuery, Data Lake, Dataflow, Docker, Kubernetes, Apache Airflow, CI/CD</t>
+          <t>Data Scientist, Generative AI, RAG, Gemini, TensorFlow, PyTorch, S3, EC2, Glue, Athena</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94efcb73c0d62620</t>
+          <t>https://www.indeed.com/viewjob?jk=acfaf9670e6dc175</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>AWS Data Scientist</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Hinge</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Redshift, BigQuery, Dataflow, Docker, Kubernetes, GitHub Actions, Terraform, Git, Databricks</t>
+          <t>Data Scientist, Generative AI, RAG, Gemini, TensorFlow, PyTorch, S3, EC2, Glue, Athena</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f8363856d6fd5ea</t>
+          <t>https://www.indeed.com/viewjob?jk=28ad8b697f6dd69d</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GCP Data Architect with 15 year's experience local to Chicago</t>
+          <t>AWS Data Scientist</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sanford AI</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.9</v>
+        <v>20</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Data Lake, Dataflow, CI/CD, Terraform, Git, Snowflake, Databricks, BigQuery</t>
+          <t>Data Scientist, Generative AI, RAG, Gemini, TensorFlow, PyTorch, S3, EC2, Glue, Athena</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcb6ec77e71bc3c8</t>
+          <t>https://www.indeed.com/viewjob?jk=fd7fe7b57ec9369c</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AWS Data Scientist</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ascendion</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.9</v>
+        <v>20</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>LangChain, RAG, S3, Glue, Redshift, Apache Airflow, Git, Snowflake, Databricks, Redshift</t>
+          <t>Data Scientist, Generative AI, RAG, Gemini, TensorFlow, PyTorch, S3, EC2, Glue, Athena</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f03c0c824aa43ad2</t>
+          <t>https://www.indeed.com/viewjob?jk=37555ae808904ac1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Java Full Stack Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>S3, Glue, Redshift, Data Lake, Kinesis, CI/CD, Terraform, Snowflake, Databricks, Redshift</t>
+          <t>Generative AI, RAG, Gemini, Kinesis, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,14 +671,14 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f631622e574168df</t>
+          <t>https://www.indeed.com/viewjob?jk=60655539a4865f8d</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Java AWS Developer (8 or Above yrs of experienced professionals)</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -706,14 +706,14 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5114b2dc892b00c6</t>
+          <t>https://www.indeed.com/viewjob?jk=767b32d92360e6ef</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GCP Cloud Architect</t>
+          <t>Associate Data Engineer- GCP</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, BigQuery, Dataflow, Kubernetes, CI/CD, Jenkins, Terraform, Git</t>
+          <t>Data Scientist, Generative AI, RAG, Gemini, BigQuery, FastAPI, CI/CD, Git, BigQuery, Kafka</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d9a604036ab5e2b</t>
+          <t>https://www.indeed.com/viewjob?jk=e9f16501863249ef</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior AWS Developer</t>
+          <t>Senior GCP Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Altumint</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lanham, MD, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,34 +766,34 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>S3, EC2, Docker, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, MySQL, Python</t>
+          <t>Data Scientist, Generative AI, RAG, Gemini, BigQuery, Dataflow, FastAPI, CI/CD, Git, BigQuery</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fed653aec24910be</t>
+          <t>https://www.indeed.com/viewjob?jk=baad7a309761de2f</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Engineer (Python &amp; React)</t>
+          <t>GCP API Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Factored</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,24 +801,24 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, FastAPI, CI/CD, Git, PostgreSQL, MySQL, NoSQL, Python</t>
+          <t>Data Scientist, Generative AI, RAG, Gemini, BigQuery, Dataflow, FastAPI, CI/CD, Git, BigQuery</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=724d0d8443bffbcf</t>
+          <t>https://www.indeed.com/viewjob?jk=7f0fe94efdf94a50</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SRE/DevOps Engineer</t>
+          <t>Senior GCP API Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -828,15 +828,15 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
+          <t>Data Scientist, Generative AI, RAG, Gemini, BigQuery, Dataflow, FastAPI, CI/CD, Git, BigQuery</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64be9beb3d73dbb9</t>
+          <t>https://www.indeed.com/viewjob?jk=67023c52c268b7ff</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>GCP API Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Pinecone, BigQuery, MLflow, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, BigQuery</t>
+          <t>Data Scientist, Generative AI, RAG, Gemini, BigQuery, Dataflow, FastAPI, CI/CD, Git, BigQuery</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58f2445240dbd78a</t>
+          <t>https://www.indeed.com/viewjob?jk=61a12b10547477fb</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Engineer, Data</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Health in Tech</t>
+          <t>Ensemble Health Partners</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Blue Ash, OH, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, PostgreSQL, MySQL, MongoDB, NoSQL, Python</t>
+          <t>Generative AI, RAG, Dataflow, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Databricks</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,14 +916,14 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f5057bd977bc6a4</t>
+          <t>https://www.indeed.com/viewjob?jk=a968331cc3ce0086</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GenAI/Data Engineer</t>
+          <t>V&amp;V Engineer - AI-Driven Testing &amp; Validation</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -933,15 +933,15 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Prompt Engineering, Git, Databricks, Python</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, TensorFlow, PyTorch, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f094c43b2df8d8a8</t>
+          <t>https://www.indeed.com/viewjob?jk=30492497a365f912</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sr. Data Engineering Consultant - Remote</t>
+          <t>GCP API Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>UnitedHealthcare</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Redshift, CI/CD, Git, Snowflake, Databricks, Redshift, Kafka, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, RAG, Gemini, BigQuery, Dataflow, FastAPI, CI/CD, Git, BigQuery</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,14 +986,14 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d70310be183ea2e</t>
+          <t>https://www.indeed.com/viewjob?jk=f8db06c11125fc14</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Gen AI/ML Data Scientist</t>
+          <t>GCP API Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1003,15 +1003,15 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, Gemini, Docker, CI/CD, Git, Python, SQL</t>
+          <t>Data Scientist, Generative AI, RAG, Gemini, BigQuery, Dataflow, FastAPI, CI/CD, Git, BigQuery</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=280501a562f0fb78</t>
+          <t>https://www.indeed.com/viewjob?jk=74bc97caa06b5ca5</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Cloud Platform)</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Amplitude</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python</t>
+          <t>Data Scientist, Generative AI, RAG, Gemini, Synapse, Data Lake, Kubernetes, AKS, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e26c106f1b8164f</t>
+          <t>https://www.indeed.com/viewjob?jk=6d628829fcaf3036</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Moda Health</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, BigQuery, Dataflow, CI/CD, Git, BigQuery, Python, R</t>
+          <t>RAG, Redshift, BigQuery, CI/CD, Git, Snowflake, BigQuery, Redshift, Power BI, Python</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,14 +1091,14 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a52c33ac5a346e1</t>
+          <t>https://www.indeed.com/viewjob?jk=d0980ce92de11d0b</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Data Engineer with Expert-level SQL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1108,15 +1108,15 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, CI/CD, Git, Databricks, Tableau, Power BI, SQL, R</t>
+          <t>Generative AI, RAG, Gemini, Redshift, BigQuery, Synapse, Git, Snowflake, BigQuery, Redshift</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17624144d4bde746</t>
+          <t>https://www.indeed.com/viewjob?jk=2dc21b544c41959b</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Cloud Security Engineer</t>
+          <t>GenAI/Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Dragonfli Group LLC</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Terraform, Git, Databricks, PySpark, Python</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Prompt Engineering, Git, Databricks, Python</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b51c0221c27e18ee</t>
+          <t>https://www.indeed.com/viewjob?jk=e871e419290249c5</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Artificial Intelligence Software Engineer (Hybrid Eligible)</t>
+          <t>GCP API Solution Architect</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Oak Ridge National Laboratory</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Oak Ridge, TN, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Copilot, Hugging Face, TensorFlow, PyTorch, CI/CD, Python</t>
+          <t>Generative AI, RAG, Gemini, BigQuery, Data Lake, Dataflow, CI/CD, Terraform, Git, BigQuery</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fe1061f779eda0d</t>
+          <t>https://www.indeed.com/viewjob?jk=653da5ce67465bb9</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Trust &amp; Safety</t>
+          <t>Agentic AI Engineer for Aerospace (Entry Level)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Hinge</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, Hugging Face, PyTorch, Kubernetes, Git, Databricks, Python, SQL</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Copilot, Docker, CI/CD, Git</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b249efe72c30be08</t>
+          <t>https://www.indeed.com/viewjob?jk=6d17895c43fdb4af</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Scientist - Commercial Analytics</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>ＡＮＧＥＬ</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Data Scientist, XGBoost, LightGBM, CI/CD, Snowflake, Databricks, PySpark, Power BI, Python, SQL</t>
+          <t>RAG, S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a183d21d1bc32a73</t>
+          <t>https://www.indeed.com/viewjob?jk=9f885cfaa350a169</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Associate Data Scientist – Finance &amp; Accounting Automation</t>
+          <t>Software Engineer Specialist</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, TensorFlow, PyTorch, Redshift, Redshift, Tableau, Power BI</t>
+          <t>Copilot, BigQuery, Dataflow, Kubernetes, CI/CD, Jenkins, Terraform, Git, BigQuery, MySQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d317baacdb2ac3fa</t>
+          <t>https://www.indeed.com/viewjob?jk=58fe1722e4dbca11</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Python Data Engineer</t>
+          <t>Senior AI Language Model Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Occidental</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, BigQuery, Git, BigQuery, Python, SQL, R, Java</t>
+          <t>LangChain, RAG, Hugging Face, Prompt Engineering, S3, EC2, Terraform, Git, NoSQL, Python</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,14 +1336,14 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=916b0eb9ca93a7a2</t>
+          <t>https://www.indeed.com/viewjob?jk=a008874ac4d2cf95</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Migration Engineer</t>
+          <t>Azure Databrick with Anaplan</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1353,15 +1353,15 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Git, Snowflake, Kafka, Python, SQL, R, Java</t>
+          <t>Generative AI, RAG, Gemini, Synapse, Data Lake, Git, Databricks, PySpark, SQL, R</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,19 +1371,19 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f01b1849bd3f7de</t>
+          <t>https://www.indeed.com/viewjob?jk=ae17f8ab37624a34</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Point Digital Finance</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1392,11 +1392,11 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Git, Databricks, PySpark, Tableau, Power BI, SQL, R, Scala</t>
+          <t>Data Scientist, RAG, Gemini, TensorFlow, PyTorch, Tableau, Power BI, Matplotlib, Seaborn, Python</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,14 +1406,14 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=794fd3442926e801</t>
+          <t>https://www.indeed.com/viewjob?jk=9977d39e76240ba7</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Migration Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1423,15 +1423,15 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Git, Snowflake, Kafka, Python, SQL, R, Java</t>
+          <t>Generative AI, RAG, Gemini, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,14 +1441,14 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df00417b3da3f42f</t>
+          <t>https://www.indeed.com/viewjob?jk=d2bf1ed112eab86b</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Migration Engineer</t>
+          <t>Google Cloud Solution Architect</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1458,15 +1458,15 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Git, Snowflake, Kafka, Python, SQL, R, Java</t>
+          <t>Generative AI, RAG, Gemini, BigQuery, Docker, Kubernetes, CI/CD, Terraform, Git, BigQuery</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24d8dcba808e253f</t>
+          <t>https://www.indeed.com/viewjob?jk=773d002c54ccd354</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Google Cloud Solution Architect</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>DRAGOS</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, NoSQL, Python, SQL, R, Scala</t>
+          <t>Generative AI, RAG, Gemini, BigQuery, Docker, Kubernetes, CI/CD, Terraform, Git, BigQuery</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7048d55ba34c919</t>
+          <t>https://www.indeed.com/viewjob?jk=01f2dcfd4ebf8840</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior QA Automation Engineer</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL, R, Java</t>
+          <t>Generative AI, RAG, Gemini, BigQuery, Dataflow, CI/CD, Terraform, Git, BigQuery, SQL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29931ba9e2678a00</t>
+          <t>https://www.indeed.com/viewjob?jk=65072011a2bf273e</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Research Assistant</t>
+          <t>Data Engineer (AWS &amp; Snowflake)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>University of North Texas</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Denton, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, XGBoost, Keras, MLflow, FastAPI, Docker, Git, Python</t>
+          <t>Data Scientist, Generative AI, RAG, Gemini, Glue, Apache Airflow, Git, Snowflake, Python, SQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=449f9b695d435059</t>
+          <t>https://www.indeed.com/viewjob?jk=aa2ed1f30d22131d</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>MLOps Data Engineer</t>
+          <t>Senior Engineer Core Infrastructure</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>JetBlue</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Long Island City, NY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, MLflow, Kubernetes, Git, Python, R, Java, Scala</t>
+          <t>RAG, Data Lake, Docker, Kubernetes, AKS, Jenkins, Terraform, Git, Databricks, Python</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,14 +1616,14 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34fcacb2f302dc22</t>
+          <t>https://www.indeed.com/viewjob?jk=35dc08cd58b4ac30</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Azure Databricks Engineer</t>
+          <t>GCP Associate Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1633,15 +1633,15 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Synapse, Git, Databricks, PySpark, SQL, R, Scala</t>
+          <t>Generative AI, RAG, Gemini, BigQuery, Data Lake, Dataflow, CI/CD, Terraform, Git, BigQuery</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c94f00b22e57d86</t>
+          <t>https://www.indeed.com/viewjob?jk=bed49777ffc66e88</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Amplitude</t>
+          <t>Data Surge</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Git, Hadoop, Python, SQL, R, Optimization, Bayesian, Hypothesis Testing</t>
+          <t>FastAPI, Docker, Kubernetes, CI/CD, Databricks, MySQL, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a44bb3451757db0b</t>
+          <t>https://www.indeed.com/viewjob?jk=366cb138963be0c6</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Gen AI Architect</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Amplitude</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RAG, S3, Kubernetes, Terraform, Git, Snowflake, Kafka, Python, R, Java</t>
+          <t>Generative AI, RAG, Gemini, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Git, Kafka</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d573a1a4fd376e26</t>
+          <t>https://www.indeed.com/viewjob?jk=aa2437ab5cb24cf0</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Adobe Commerce Full Stack Engineer</t>
+          <t>Teamcenter Agentic Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Asset Marketing Services</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Eagan, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Git, MySQL, SQL, R, Java, Scala, Optimization</t>
+          <t>Generative AI, LangChain, RAG, Gemini, Copilot, TensorFlow, PyTorch, Git, Python, R</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16a89d83a06c5742</t>
+          <t>https://www.indeed.com/viewjob?jk=ed507cb1ccfda89c</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Akkadian Labs</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Hoboken, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Python, R, Scala</t>
+          <t>Generative AI, RAG, Gemini, BigQuery, Dataflow, Git, BigQuery, PySpark, Python, SQL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56e78fa05eac6e15</t>
+          <t>https://www.indeed.com/viewjob?jk=19de4aef9559932c</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Engineer, (L2) CDP</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Kafka, PostgreSQL, Python, SQL, R, Java, Scala</t>
+          <t>Generative AI, RAG, Gemini, BigQuery, Dataflow, Git, BigQuery, PySpark, Python, SQL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38ff081155f4529b</t>
+          <t>https://www.indeed.com/viewjob?jk=c0220973153f5e26</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Tool / Platform Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Clearlink</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Data Lake, Git, NoSQL, Python, SQL, R, Java, Scala</t>
+          <t>Generative AI, RAG, Gemini, BigQuery, Dataflow, Git, BigQuery, Python, SQL, R</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fcc1c840bd1c22a</t>
+          <t>https://www.indeed.com/viewjob?jk=369143f108dd577d</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Chicago, Atlanta, Boston)</t>
+          <t>Senior CloudOps Engineer - Life Sciences</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>8th Light</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>LangChain, RAG, CI/CD, Git, Databricks, Python, SQL, R, Java, Scala</t>
+          <t>Generative AI, RAG, Gemini, Kubernetes, AKS, CI/CD, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23a94ad39c7ec6bf</t>
+          <t>https://www.indeed.com/viewjob?jk=ff101b2f8a8d2a0b</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>IT Data Science Engineer</t>
+          <t>Data Migration Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SubCom</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Newington, NH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Synapse, Data Lake, CI/CD, Git, Power BI, SQL, R, Scala</t>
+          <t>Generative AI, RAG, Gemini, Git, Snowflake, Kafka, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,67 +1931,67 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c70b005bd5571ce9</t>
+          <t>https://www.indeed.com/viewjob?jk=4b2df5fe971badc2</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Junior Python Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Altumint</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Lanham, MD, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>FastAPI, Docker, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, Python, SQL, R</t>
+          <t>RAG, Synapse, CI/CD, Terraform, Git, Databricks, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56bf68959ce66852</t>
+          <t>https://www.indeed.com/viewjob?jk=11bb6883564eae74</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SCADA Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Git, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Synapse, CI/CD, Terraform, Git, Databricks, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43926177b43175c1</t>
+          <t>https://www.indeed.com/viewjob?jk=3d67068993909e1d</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Referral Only- GCP Solution Architect</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Kubernetes, CI/CD, Terraform, Git, R, Scala</t>
+          <t>RAG, Synapse, CI/CD, Terraform, Git, Databricks, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73fabb58ae40bd7f</t>
+          <t>https://www.indeed.com/viewjob?jk=afd00ed67e04bb32</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>SDET (POS Automation)</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, CI/CD, Git, Python, R, Java, Scala</t>
+          <t>RAG, Synapse, CI/CD, Terraform, Git, Databricks, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31ac04dd37bf808a</t>
+          <t>https://www.indeed.com/viewjob?jk=e9fbf2318173a6e1</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Embedded Software Developer for RDK-B</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Docker, CI/CD, Git, Python, R, Scala</t>
+          <t>RAG, Synapse, CI/CD, Terraform, Git, Databricks, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8da5199081e49bcd</t>
+          <t>https://www.indeed.com/viewjob?jk=1191a515fb7b159c</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Software Engineer Intern (AI/ML) - Fall 2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Menlo Park, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>CI/CD, MongoDB, NoSQL, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>Generative AI, RAG, Cortex, PyTorch, Snowflake, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee77fd9889843e4c</t>
+          <t>https://www.indeed.com/viewjob?jk=f1980a9fdabf1555</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Research Engineer - Voleon Securities</t>
+          <t>Senior UI Developer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>The Voleon Group</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Berkeley, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RAG, PyTorch, MySQL, MongoDB, Cassandra, Python, SQL, R, Optimization</t>
+          <t>Generative AI, RAG, Gemini, S3, CI/CD, Git, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a24e5d5893a94fec</t>
+          <t>https://www.indeed.com/viewjob?jk=6e779111f137e927</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Research Engineer - Voleon Securities</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>The Voleon Group</t>
+          <t>Further</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RAG, PyTorch, MySQL, MongoDB, Cassandra, Python, SQL, R, Optimization</t>
+          <t>RAG, Pinecone, BigQuery, Kinesis, Snowflake, Databricks, BigQuery, Kafka, SQL, R</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06c817f70e864a3d</t>
+          <t>https://www.indeed.com/viewjob?jk=cd11cd8ab523106f</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Java Full Stack with GenAI</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Vendelux</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, Python, SQL, R, Scala</t>
+          <t>Generative AI, RAG, Gemini, Prompt Engineering, Git, NoSQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3bd484668de1f94</t>
+          <t>https://www.indeed.com/viewjob?jk=27c2d61e7d2cade9</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Vendelux</t>
+          <t>Amplitude</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, Python, SQL, R, Scala</t>
+          <t>RAG, S3, Kubernetes, Terraform, Git, Snowflake, Kafka, Python, R, Java</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed3ae1a38cca1ea2</t>
+          <t>https://www.indeed.com/viewjob?jk=a0fc65d50bb5f847</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Fire &amp; Police Pension Association</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, AKS, CI/CD, Terraform, Git, Python, R</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, Gemini, Git, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,42 +2316,777 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81e9dbcfe4537ee6</t>
+          <t>https://www.indeed.com/viewjob?jk=4b26c8f196a07832</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
+          <t>Data Engineer - Databricks</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, CI/CD, Git, Databricks, PySpark, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=49b0aa2be5209d6a</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Senior APIM / CXI Engineer</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, Docker, Kubernetes, CI/CD, Terraform, Git, R, Scala</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=354399ae4b2a367a</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Associate Data Scientist, New College Grad - 2026</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Jobs for Humanity</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>San Juan, PR, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, Git, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8ae72b7face71d88</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Sr. Analysts</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>TransUnion</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, BigQuery, BigQuery, Python, SQL, R, Optimization, Bayesian, Hypothesis Testing</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fddf5c14e528f213</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Gemini, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3ee18cd6724ac2a7</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Emerging Technology</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Burbank, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, NoSQL, Python, SQL, R, Scala, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a7194b9b88caffad</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Senior Mobile Developer</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>10</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, Copilot, Prompt Engineering, Git, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e28ecbf835a2c904</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>USA - Tax - Americas Tax Technology Group (ATTG) - Engineer - Assistant Analyst</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>EY</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>10</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, AKS, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b24f72efabd36d55</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Dot Net/SSRS developer - Software Engineer</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>10</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, S3, EC2, Git, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=70d4c2757af5bcf0</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>SCADA Engineer - Ignition Platform</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>10</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, Git, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=18c00af97067b174</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>FinOps Engineer - GCP</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>10</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, BigQuery, Git, BigQuery, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=110c73e042f0f3f1</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>React.JS + GenAI Developer</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>10</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, S3, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d8ac5cae1c564da0</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Mobile Application Architect</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>10</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, CI/CD, Git, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a028625ced6021c6</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Angular Developer in Dallas, TX</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>10</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, Docker, Jenkins, Git, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fba681f8e2e43919</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Software Engineer- Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>10</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8f739a0a13fc85c7</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Sr. Dot Net Developer</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>10</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, Git, NoSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9b178f63b0791029</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Embedded Software Developer for RDK-B</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Santa Clara, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>10</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, Docker, CI/CD, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5f1669cc4b1eb3c3</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>AI/ML Engineer Sr (mid-career)</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Lockheed Martin</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>PR, US USA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>10</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e120cd40228e60f7</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>AI/ML Engineer Sr (mid-career)</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Lockheed Martin</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>PR, US USA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>10</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f70cfbc830d3617d</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>AI/ML Engineer Sr (mid-career)</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Lockheed Martin</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>PR, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>10</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a0110b968b713cf4</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Software Engineer - GenAI (Teradyne, North Reading)</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Teradyne</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>North Reading, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>10</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=43e9826714560d67</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
           <t>Data Scientist</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Zoom Communications</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
         <v>10</v>
       </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, MLflow, Snowflake, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f4f7bb7f6cc5ed4e</t>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Gemini, Git, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2266ec13932d9217</t>
         </is>
       </c>
     </row>
